--- a/English11.xlsx
+++ b/English11.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="uHSSVpASoHBb8IRN/mcQbDrVjovYfWjMDws4AIlLSdI="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="niLCEALgr/ApZagn6WVZULanzAk2C+k8vZLcPdwEfTs="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="410">
   <si>
     <t>id</t>
   </si>
@@ -43,7 +43,19 @@
  D.a'ou'ntry</t>
   </si>
   <si>
+    <t>primary</t>
+  </si>
+  <si>
     <t>D</t>
+  </si>
+  <si>
+    <t>compulsory</t>
+  </si>
+  <si>
+    <t>national</t>
+  </si>
+  <si>
+    <t>second</t>
   </si>
   <si>
     <t>Choose the word which has the quoted part pronounced differently from the rest. 
@@ -87,19 +99,7 @@
  D. that</t>
   </si>
   <si>
-    <t>primary</t>
-  </si>
-  <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>compulsory</t>
-  </si>
-  <si>
-    <t>national</t>
-  </si>
-  <si>
-    <t>second</t>
   </si>
   <si>
     <t>Thuy’s class is different ________ other classes because the children are disabled. 
@@ -1965,8 +1965,11 @@
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2">
         <v>1.0</v>
@@ -1976,763 +1979,733 @@
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="2">
-        <v>2.0</v>
-      </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="2" t="s">
+    </row>
+    <row r="6" ht="12.75" customHeight="1">
+      <c r="C6" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E5" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="6" ht="12.75" customHeight="1">
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2">
-        <v>4.0</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="E7" s="2">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3.0</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="B12" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="2">
-        <v>7.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
+      <c r="B15" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C15" s="2" t="s">
-        <v>24</v>
+        <v>7</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2">
+        <v>4.0</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="B16" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="C16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="E16" s="2">
-        <v>8.0</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
+      <c r="B19" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="C19" s="2" t="s">
-        <v>29</v>
+        <v>7</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="2">
+        <v>5.0</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="B20" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="E20" s="2">
-        <v>9.0</v>
       </c>
     </row>
     <row r="21" ht="12.75" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
+      <c r="A23" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="C23" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
-      <c r="B24" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="C24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="2">
-        <v>10.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
       <c r="C25" s="2" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
       <c r="C26" s="2" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
+      <c r="B27" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="C27" s="2" t="s">
-        <v>39</v>
+        <v>21</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="2">
+        <v>7.0</v>
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="C28" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0.0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" ht="12.75" customHeight="1">
       <c r="C29" s="2" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="C30" s="2" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" ht="12.75" customHeight="1">
+      <c r="B31" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="C31" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="2">
+        <v>8.0</v>
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="B32" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="C32" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="2">
-        <v>12.0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="C33" s="2" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1">
       <c r="C34" s="2" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
+      <c r="B35" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="C35" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="2">
+        <v>9.0</v>
       </c>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="B36" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="C36" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" s="2">
-        <v>13.0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="C37" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
       <c r="C38" s="2" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" ht="12.75" customHeight="1">
+      <c r="B39" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C39" s="2" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2">
+        <v>10.0</v>
       </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="B40" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="C40" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="2">
-        <v>14.0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="C41" s="2" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="C42" s="2" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" ht="12.75" customHeight="1">
+      <c r="A43" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="C43" s="2" t="s">
-        <v>59</v>
+        <v>41</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="B44" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="C44" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="2">
-        <v>15.0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1">
       <c r="C45" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1">
       <c r="C46" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1">
+      <c r="B47" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="C47" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="2">
+        <v>12.0</v>
       </c>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="C48" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="2">
-        <v>16.0</v>
-      </c>
-      <c r="F48" s="2">
-        <v>0.0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1">
       <c r="C49" s="2" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" ht="12.75" customHeight="1">
       <c r="C50" s="2" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" ht="12.75" customHeight="1">
+      <c r="B51" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="C51" s="2" t="s">
-        <v>69</v>
+        <v>51</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" s="2">
+        <v>13.0</v>
       </c>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="B52" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="C52" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="2">
-        <v>17.0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" ht="12.75" customHeight="1">
       <c r="C53" s="2" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" ht="12.75" customHeight="1">
       <c r="C54" s="2" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" ht="12.75" customHeight="1">
+      <c r="B55" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="C55" s="2" t="s">
-        <v>71</v>
+        <v>56</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="2">
+        <v>14.0</v>
       </c>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="B56" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="C56" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="2">
-        <v>18.0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="1">
       <c r="C57" s="2" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" ht="12.75" customHeight="1">
       <c r="C58" s="2" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" ht="12.75" customHeight="1">
+      <c r="B59" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="C59" s="2" t="s">
-        <v>76</v>
+        <v>61</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="2">
+        <v>15.0</v>
       </c>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="B60" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C60" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="2">
-        <v>19.0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="1">
       <c r="C61" s="2" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" ht="12.75" customHeight="1">
       <c r="C62" s="2" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63" ht="12.75" customHeight="1">
+      <c r="A63" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="C63" s="2" t="s">
-        <v>81</v>
+        <v>66</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="F63" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="B64" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="C64" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" s="2">
-        <v>20.0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" ht="12.75" customHeight="1">
       <c r="C65" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" ht="12.75" customHeight="1">
       <c r="C66" s="2" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" ht="12.75" customHeight="1">
+      <c r="B67" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="C67" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="D67" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="2">
+        <v>17.0</v>
+      </c>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="A68" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="C68" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="F68" s="2">
-        <v>0.0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" ht="12.75" customHeight="1">
       <c r="C69" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" ht="12.75" customHeight="1">
       <c r="C70" s="2" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" ht="12.75" customHeight="1">
+      <c r="B71" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="C71" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E71" s="2">
+        <v>18.0</v>
       </c>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="B72" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="C72" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E72" s="2">
-        <v>22.0</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" ht="12.75" customHeight="1">
       <c r="C73" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" ht="12.75" customHeight="1">
       <c r="C74" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="1">
+      <c r="B75" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="C75" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E75" s="2">
+        <v>19.0</v>
       </c>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="B76" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="C76" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E76" s="2">
-        <v>23.0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77" ht="12.75" customHeight="1">
       <c r="C77" s="2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" ht="12.75" customHeight="1">
       <c r="C78" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" ht="12.75" customHeight="1">
+      <c r="B79" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="C79" s="2" t="s">
-        <v>93</v>
+        <v>34</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E79" s="2">
+        <v>20.0</v>
       </c>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="B80" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="C80" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E80" s="2">
-        <v>24.0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="81" ht="12.75" customHeight="1">
       <c r="C81" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="82" ht="12.75" customHeight="1">
       <c r="C82" s="2" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83" ht="12.75" customHeight="1">
+      <c r="A83" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="C83" s="2" t="s">
-        <v>96</v>
+        <v>44</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="F83" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="84" ht="12.75" customHeight="1">
-      <c r="B84" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="C84" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E84" s="2">
-        <v>25.0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="85" ht="12.75" customHeight="1">
       <c r="C85" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="86" ht="12.75" customHeight="1">
       <c r="C86" s="2" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87" ht="12.75" customHeight="1">
+      <c r="B87" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="C87" s="2" t="s">
-        <v>71</v>
+        <v>86</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" s="2">
+        <v>22.0</v>
       </c>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="A88" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="C88" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="2">
-        <v>26.0</v>
-      </c>
-      <c r="F88" s="2">
-        <v>0.0</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89" ht="12.75" customHeight="1">
       <c r="C89" s="2" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90" ht="12.75" customHeight="1">
       <c r="C90" s="2" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
     </row>
     <row r="91" ht="12.75" customHeight="1">
+      <c r="B91" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="C91" s="2" t="s">
-        <v>103</v>
+        <v>90</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E91" s="2">
+        <v>23.0</v>
       </c>
     </row>
     <row r="92" ht="12.75" customHeight="1">
-      <c r="B92" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="C92" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E92" s="2">
-        <v>27.0</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93" ht="12.75" customHeight="1">
       <c r="C93" s="2" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94" ht="12.75" customHeight="1">
       <c r="C94" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95" ht="12.75" customHeight="1">
+      <c r="B95" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="C95" s="2" t="s">
-        <v>96</v>
+        <v>63</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E95" s="2">
+        <v>24.0</v>
       </c>
     </row>
     <row r="96" ht="12.75" customHeight="1">
-      <c r="B96" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="C96" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E96" s="2">
-        <v>28.0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="97" ht="12.75" customHeight="1">
       <c r="C97" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" ht="12.75" customHeight="1">
       <c r="C98" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" ht="12.75" customHeight="1">
+      <c r="B99" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E99" s="2">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="100" ht="12.75" customHeight="1">
+      <c r="C100" s="2" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="99" ht="12.75" customHeight="1">
-      <c r="C99" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="100" ht="12.75" customHeight="1">
-      <c r="B100" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E100" s="2">
-        <v>29.0</v>
       </c>
     </row>
     <row r="101" ht="12.75" customHeight="1">
       <c r="C101" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102" ht="12.75" customHeight="1">
@@ -2741,1723 +2714,1723 @@
       </c>
     </row>
     <row r="103" ht="12.75" customHeight="1">
+      <c r="A103" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="C103" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E103" s="2">
+        <v>26.0</v>
+      </c>
+      <c r="F103" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="104" ht="12.75" customHeight="1">
-      <c r="B104" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="C104" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="2">
-        <v>30.0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="105" ht="12.75" customHeight="1">
       <c r="C105" s="2" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106" ht="12.75" customHeight="1">
       <c r="C106" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="107" ht="12.75" customHeight="1">
+      <c r="B107" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="C107" s="2" t="s">
-        <v>112</v>
+        <v>99</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" s="2">
+        <v>27.0</v>
       </c>
     </row>
     <row r="108" ht="12.75" customHeight="1">
-      <c r="A108" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="C108" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E108" s="2">
-        <v>31.0</v>
-      </c>
-      <c r="F108" s="2">
-        <v>0.0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" ht="12.75" customHeight="1">
       <c r="C109" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="110" ht="12.75" customHeight="1">
       <c r="C110" s="2" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="111" ht="12.75" customHeight="1">
+      <c r="B111" s="2" t="s">
+        <v>106</v>
+      </c>
       <c r="C111" s="2" t="s">
-        <v>117</v>
+        <v>98</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E111" s="2">
+        <v>28.0</v>
       </c>
     </row>
     <row r="112" ht="12.75" customHeight="1">
-      <c r="B112" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="C112" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" s="2">
-        <v>32.0</v>
+        <v>99</v>
       </c>
     </row>
     <row r="113" ht="12.75" customHeight="1">
       <c r="C113" s="2" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114" ht="12.75" customHeight="1">
       <c r="C114" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
     </row>
     <row r="115" ht="12.75" customHeight="1">
+      <c r="B115" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="C115" s="2" t="s">
-        <v>122</v>
+        <v>32</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E115" s="2">
+        <v>29.0</v>
       </c>
     </row>
     <row r="116" ht="12.75" customHeight="1">
-      <c r="B116" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="C116" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E116" s="2">
-        <v>33.0</v>
+        <v>107</v>
       </c>
     </row>
     <row r="117" ht="12.75" customHeight="1">
       <c r="C117" s="2" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
     </row>
     <row r="118" ht="12.75" customHeight="1">
       <c r="C118" s="2" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
     </row>
     <row r="119" ht="12.75" customHeight="1">
+      <c r="B119" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="C119" s="2" t="s">
-        <v>7</v>
+        <v>110</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E119" s="2">
+        <v>30.0</v>
       </c>
     </row>
     <row r="120" ht="12.75" customHeight="1">
-      <c r="B120" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="C120" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E120" s="2">
-        <v>34.0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="121" ht="12.75" customHeight="1">
       <c r="C121" s="2" t="s">
-        <v>9</v>
+        <v>111</v>
       </c>
     </row>
     <row r="122" ht="12.75" customHeight="1">
       <c r="C122" s="2" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
     </row>
     <row r="123" ht="12.75" customHeight="1">
+      <c r="A123" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="C123" s="2" t="s">
-        <v>7</v>
+        <v>114</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E123" s="2">
+        <v>31.0</v>
+      </c>
+      <c r="F123" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="124" ht="12.75" customHeight="1">
-      <c r="B124" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="C124" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E124" s="2">
-        <v>35.0</v>
+        <v>115</v>
       </c>
     </row>
     <row r="125" ht="12.75" customHeight="1">
       <c r="C125" s="2" t="s">
-        <v>9</v>
+        <v>116</v>
       </c>
     </row>
     <row r="126" ht="12.75" customHeight="1">
       <c r="C126" s="2" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
     </row>
     <row r="127" ht="12.75" customHeight="1">
+      <c r="B127" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="C127" s="2" t="s">
-        <v>7</v>
+        <v>119</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E127" s="2">
+        <v>32.0</v>
       </c>
     </row>
     <row r="128" ht="12.75" customHeight="1">
-      <c r="A128" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="C128" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E128" s="2">
-        <v>36.0</v>
-      </c>
-      <c r="F128" s="2">
-        <v>0.0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="129" ht="12.75" customHeight="1">
       <c r="C129" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="130" ht="12.75" customHeight="1">
       <c r="C130" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="131" ht="12.75" customHeight="1">
+      <c r="B131" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="C131" s="2" t="s">
-        <v>130</v>
+        <v>19</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E131" s="2">
+        <v>33.0</v>
       </c>
     </row>
     <row r="132" ht="12.75" customHeight="1">
-      <c r="B132" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="C132" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E132" s="2">
-        <v>37.0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133" ht="12.75" customHeight="1">
       <c r="C133" s="2" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134" ht="12.75" customHeight="1">
       <c r="C134" s="2" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" ht="12.75" customHeight="1">
+      <c r="B135" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="C135" s="2" t="s">
-        <v>135</v>
+        <v>19</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E135" s="2">
+        <v>34.0</v>
       </c>
     </row>
     <row r="136" ht="12.75" customHeight="1">
-      <c r="B136" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="C136" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E136" s="2">
-        <v>38.0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137" ht="12.75" customHeight="1">
       <c r="C137" s="2" t="s">
-        <v>138</v>
+        <v>15</v>
       </c>
     </row>
     <row r="138" ht="12.75" customHeight="1">
       <c r="C138" s="2" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139" ht="12.75" customHeight="1">
+      <c r="B139" s="2" t="s">
+        <v>125</v>
+      </c>
       <c r="C139" s="2" t="s">
-        <v>140</v>
+        <v>19</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E139" s="2">
+        <v>35.0</v>
       </c>
     </row>
     <row r="140" ht="12.75" customHeight="1">
-      <c r="B140" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="C140" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E140" s="2">
-        <v>39.0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141" ht="12.75" customHeight="1">
       <c r="C141" s="2" t="s">
-        <v>143</v>
+        <v>15</v>
       </c>
     </row>
     <row r="142" ht="12.75" customHeight="1">
       <c r="C142" s="2" t="s">
-        <v>144</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" ht="12.75" customHeight="1">
+      <c r="A143" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="C143" s="2" t="s">
-        <v>145</v>
+        <v>127</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E143" s="2">
+        <v>36.0</v>
+      </c>
+      <c r="F143" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="144" ht="12.75" customHeight="1">
-      <c r="B144" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="C144" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E144" s="2">
-        <v>40.0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="145" ht="12.75" customHeight="1">
       <c r="C145" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
     </row>
     <row r="146" ht="12.75" customHeight="1">
       <c r="C146" s="2" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
     </row>
     <row r="147" ht="12.75" customHeight="1">
+      <c r="B147" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="C147" s="2" t="s">
-        <v>150</v>
+        <v>132</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E147" s="2">
+        <v>37.0</v>
       </c>
     </row>
     <row r="148" ht="12.75" customHeight="1">
-      <c r="A148" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="C148" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E148" s="2">
-        <v>41.0</v>
-      </c>
-      <c r="F148" s="2">
-        <v>0.0</v>
+        <v>133</v>
       </c>
     </row>
     <row r="149" ht="12.75" customHeight="1">
       <c r="C149" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
     </row>
     <row r="150" ht="12.75" customHeight="1">
       <c r="C150" s="2" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="151" ht="12.75" customHeight="1">
+      <c r="B151" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="C151" s="2" t="s">
-        <v>155</v>
+        <v>137</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E151" s="2">
+        <v>38.0</v>
       </c>
     </row>
     <row r="152" ht="12.75" customHeight="1">
-      <c r="B152" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="C152" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E152" s="2">
-        <v>42.0</v>
+        <v>138</v>
       </c>
     </row>
     <row r="153" ht="12.75" customHeight="1">
       <c r="C153" s="2" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
     </row>
     <row r="154" ht="12.75" customHeight="1">
       <c r="C154" s="2" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
     </row>
     <row r="155" ht="12.75" customHeight="1">
+      <c r="B155" s="2" t="s">
+        <v>141</v>
+      </c>
       <c r="C155" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E155" s="2">
+        <v>39.0</v>
       </c>
     </row>
     <row r="156" ht="12.75" customHeight="1">
-      <c r="B156" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="C156" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E156" s="2">
-        <v>43.0</v>
+        <v>143</v>
       </c>
     </row>
     <row r="157" ht="12.75" customHeight="1">
       <c r="C157" s="2" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
     </row>
     <row r="158" ht="12.75" customHeight="1">
       <c r="C158" s="2" t="s">
-        <v>102</v>
+        <v>145</v>
       </c>
     </row>
     <row r="159" ht="12.75" customHeight="1">
+      <c r="B159" s="2" t="s">
+        <v>146</v>
+      </c>
       <c r="C159" s="2" t="s">
-        <v>32</v>
+        <v>147</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E159" s="2">
+        <v>40.0</v>
       </c>
     </row>
     <row r="160" ht="12.75" customHeight="1">
-      <c r="B160" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="C160" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D160" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E160" s="2">
-        <v>44.0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="161" ht="12.75" customHeight="1">
       <c r="C161" s="2" t="s">
-        <v>31</v>
+        <v>149</v>
       </c>
     </row>
     <row r="162" ht="12.75" customHeight="1">
       <c r="C162" s="2" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
     </row>
     <row r="163" ht="12.75" customHeight="1">
+      <c r="A163" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="C163" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E163" s="2">
+        <v>41.0</v>
+      </c>
+      <c r="F163" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="164" ht="12.75" customHeight="1">
-      <c r="B164" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="C164" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E164" s="2">
-        <v>45.0</v>
+        <v>153</v>
       </c>
     </row>
     <row r="165" ht="12.75" customHeight="1">
       <c r="C165" s="2" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
     </row>
     <row r="166" ht="12.75" customHeight="1">
       <c r="C166" s="2" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
     </row>
     <row r="167" ht="12.75" customHeight="1">
+      <c r="B167" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="C167" s="2" t="s">
-        <v>170</v>
+        <v>157</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E167" s="2">
+        <v>42.0</v>
       </c>
     </row>
     <row r="168" ht="12.75" customHeight="1">
-      <c r="A168" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="C168" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E168" s="2">
-        <v>46.0</v>
-      </c>
-      <c r="F168" s="2">
-        <v>0.0</v>
+        <v>158</v>
       </c>
     </row>
     <row r="169" ht="12.75" customHeight="1">
       <c r="C169" s="2" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
     </row>
     <row r="170" ht="12.75" customHeight="1">
       <c r="C170" s="2" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
     </row>
     <row r="171" ht="12.75" customHeight="1">
+      <c r="B171" s="2" t="s">
+        <v>161</v>
+      </c>
       <c r="C171" s="2" t="s">
-        <v>175</v>
+        <v>71</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E171" s="2">
+        <v>43.0</v>
       </c>
     </row>
     <row r="172" ht="12.75" customHeight="1">
-      <c r="B172" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="C172" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E172" s="2">
-        <v>47.0</v>
+        <v>103</v>
       </c>
     </row>
     <row r="173" ht="12.75" customHeight="1">
       <c r="C173" s="2" t="s">
-        <v>178</v>
+        <v>102</v>
       </c>
     </row>
     <row r="174" ht="12.75" customHeight="1">
       <c r="C174" s="2" t="s">
-        <v>179</v>
+        <v>32</v>
       </c>
     </row>
     <row r="175" ht="12.75" customHeight="1">
+      <c r="B175" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="C175" s="2" t="s">
-        <v>180</v>
+        <v>163</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E175" s="2">
+        <v>44.0</v>
       </c>
     </row>
     <row r="176" ht="12.75" customHeight="1">
-      <c r="B176" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="C176" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E176" s="2">
-        <v>48.0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="177" ht="12.75" customHeight="1">
       <c r="C177" s="2" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
     </row>
     <row r="178" ht="12.75" customHeight="1">
       <c r="C178" s="2" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
     </row>
     <row r="179" ht="12.75" customHeight="1">
+      <c r="B179" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="C179" s="2" t="s">
-        <v>185</v>
+        <v>167</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45.0</v>
       </c>
     </row>
     <row r="180" ht="12.75" customHeight="1">
-      <c r="B180" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="C180" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E180" s="2">
-        <v>49.0</v>
+        <v>168</v>
       </c>
     </row>
     <row r="181" ht="12.75" customHeight="1">
       <c r="C181" s="2" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
     </row>
     <row r="182" ht="12.75" customHeight="1">
       <c r="C182" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
     </row>
     <row r="183" ht="12.75" customHeight="1">
+      <c r="A183" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>171</v>
+      </c>
       <c r="C183" s="2" t="s">
-        <v>190</v>
+        <v>172</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E183" s="2">
+        <v>46.0</v>
+      </c>
+      <c r="F183" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="184" ht="12.75" customHeight="1">
-      <c r="B184" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="C184" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E184" s="2">
-        <v>50.0</v>
+        <v>173</v>
       </c>
     </row>
     <row r="185" ht="12.75" customHeight="1">
       <c r="C185" s="2" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
     </row>
     <row r="186" ht="12.75" customHeight="1">
       <c r="C186" s="2" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
     </row>
     <row r="187" ht="12.75" customHeight="1">
+      <c r="B187" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="C187" s="2" t="s">
-        <v>195</v>
+        <v>177</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E187" s="2">
+        <v>47.0</v>
       </c>
     </row>
     <row r="188" ht="12.75" customHeight="1">
-      <c r="A188" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>196</v>
-      </c>
       <c r="C188" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D188" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E188" s="2">
-        <v>51.0</v>
-      </c>
-      <c r="F188" s="2">
-        <v>0.0</v>
+        <v>178</v>
       </c>
     </row>
     <row r="189" ht="12.75" customHeight="1">
       <c r="C189" s="2" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
     </row>
     <row r="190" ht="12.75" customHeight="1">
       <c r="C190" s="2" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
     </row>
     <row r="191" ht="12.75" customHeight="1">
+      <c r="B191" s="2" t="s">
+        <v>181</v>
+      </c>
       <c r="C191" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E191" s="2">
+        <v>48.0</v>
       </c>
     </row>
     <row r="192" ht="12.75" customHeight="1">
-      <c r="B192" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="C192" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E192" s="2">
-        <v>52.0</v>
+        <v>183</v>
       </c>
     </row>
     <row r="193" ht="12.75" customHeight="1">
       <c r="C193" s="2" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
     </row>
     <row r="194" ht="12.75" customHeight="1">
       <c r="C194" s="2" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
     </row>
     <row r="195" ht="12.75" customHeight="1">
+      <c r="B195" s="2" t="s">
+        <v>186</v>
+      </c>
       <c r="C195" s="2" t="s">
-        <v>205</v>
+        <v>187</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E195" s="2">
+        <v>49.0</v>
       </c>
     </row>
     <row r="196" ht="12.75" customHeight="1">
-      <c r="B196" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="C196" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E196" s="2">
-        <v>53.0</v>
+        <v>188</v>
       </c>
     </row>
     <row r="197" ht="12.75" customHeight="1">
       <c r="C197" s="2" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
     </row>
     <row r="198" ht="12.75" customHeight="1">
       <c r="C198" s="2" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
     </row>
     <row r="199" ht="12.75" customHeight="1">
+      <c r="B199" s="2" t="s">
+        <v>191</v>
+      </c>
       <c r="C199" s="2" t="s">
-        <v>210</v>
+        <v>192</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E199" s="2">
+        <v>50.0</v>
       </c>
     </row>
     <row r="200" ht="12.75" customHeight="1">
-      <c r="B200" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="C200" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E200" s="2">
-        <v>54.0</v>
+        <v>193</v>
       </c>
     </row>
     <row r="201" ht="12.75" customHeight="1">
       <c r="C201" s="2" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
     </row>
     <row r="202" ht="12.75" customHeight="1">
       <c r="C202" s="2" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
     </row>
     <row r="203" ht="12.75" customHeight="1">
+      <c r="A203" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>196</v>
+      </c>
       <c r="C203" s="2" t="s">
-        <v>214</v>
+        <v>197</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E203" s="2">
+        <v>51.0</v>
+      </c>
+      <c r="F203" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="204" ht="12.75" customHeight="1">
-      <c r="B204" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="C204" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D204" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E204" s="2">
-        <v>55.0</v>
+        <v>198</v>
       </c>
     </row>
     <row r="205" ht="12.75" customHeight="1">
       <c r="C205" s="2" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="206" ht="12.75" customHeight="1">
       <c r="C206" s="2" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="207" ht="12.75" customHeight="1">
+      <c r="B207" s="2" t="s">
+        <v>201</v>
+      </c>
       <c r="C207" s="2" t="s">
-        <v>219</v>
+        <v>202</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E207" s="2">
+        <v>52.0</v>
       </c>
     </row>
     <row r="208" ht="12.75" customHeight="1">
-      <c r="A208" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="C208" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E208" s="2">
-        <v>56.0</v>
-      </c>
-      <c r="F208" s="2">
-        <v>0.0</v>
+        <v>203</v>
       </c>
     </row>
     <row r="209" ht="12.75" customHeight="1">
       <c r="C209" s="2" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
     </row>
     <row r="210" ht="12.75" customHeight="1">
       <c r="C210" s="2" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
     </row>
     <row r="211" ht="12.75" customHeight="1">
+      <c r="B211" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="C211" s="2" t="s">
-        <v>224</v>
+        <v>207</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E211" s="2">
+        <v>53.0</v>
       </c>
     </row>
     <row r="212" ht="12.75" customHeight="1">
-      <c r="B212" s="2" t="s">
-        <v>225</v>
-      </c>
       <c r="C212" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E212" s="2">
-        <v>57.0</v>
+        <v>208</v>
       </c>
     </row>
     <row r="213" ht="12.75" customHeight="1">
       <c r="C213" s="2" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
     </row>
     <row r="214" ht="12.75" customHeight="1">
       <c r="C214" s="2" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
     </row>
     <row r="215" ht="12.75" customHeight="1">
+      <c r="B215" s="2" t="s">
+        <v>211</v>
+      </c>
       <c r="C215" s="2" t="s">
-        <v>229</v>
+        <v>114</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E215" s="2">
+        <v>54.0</v>
       </c>
     </row>
     <row r="216" ht="12.75" customHeight="1">
-      <c r="B216" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="C216" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E216" s="2">
-        <v>58.0</v>
+        <v>212</v>
       </c>
     </row>
     <row r="217" ht="12.75" customHeight="1">
       <c r="C217" s="2" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
     </row>
     <row r="218" ht="12.75" customHeight="1">
       <c r="C218" s="2" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
     </row>
     <row r="219" ht="12.75" customHeight="1">
+      <c r="B219" s="2" t="s">
+        <v>215</v>
+      </c>
       <c r="C219" s="2" t="s">
-        <v>234</v>
+        <v>216</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E219" s="2">
+        <v>55.0</v>
       </c>
     </row>
     <row r="220" ht="12.75" customHeight="1">
-      <c r="B220" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="C220" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E220" s="2">
-        <v>59.0</v>
+        <v>217</v>
       </c>
     </row>
     <row r="221" ht="12.75" customHeight="1">
       <c r="C221" s="2" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
     </row>
     <row r="222" ht="12.75" customHeight="1">
       <c r="C222" s="2" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
     </row>
     <row r="223" ht="12.75" customHeight="1">
+      <c r="A223" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>220</v>
+      </c>
       <c r="C223" s="2" t="s">
-        <v>239</v>
+        <v>221</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E223" s="2">
+        <v>56.0</v>
+      </c>
+      <c r="F223" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="224" ht="12.75" customHeight="1">
-      <c r="B224" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="C224" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E224" s="2">
-        <v>60.0</v>
+        <v>222</v>
       </c>
     </row>
     <row r="225" ht="12.75" customHeight="1">
       <c r="C225" s="2" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
     </row>
     <row r="226" ht="12.75" customHeight="1">
       <c r="C226" s="2" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
     </row>
     <row r="227" ht="12.75" customHeight="1">
+      <c r="B227" s="2" t="s">
+        <v>225</v>
+      </c>
       <c r="C227" s="2" t="s">
-        <v>244</v>
+        <v>226</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E227" s="2">
+        <v>57.0</v>
       </c>
     </row>
     <row r="228" ht="12.75" customHeight="1">
-      <c r="A228" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="C228" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D228" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E228" s="2">
-        <v>61.0</v>
-      </c>
-      <c r="F228" s="2">
-        <v>0.0</v>
+        <v>227</v>
       </c>
     </row>
     <row r="229" ht="12.75" customHeight="1">
       <c r="C229" s="2" t="s">
-        <v>31</v>
+        <v>228</v>
       </c>
     </row>
     <row r="230" ht="12.75" customHeight="1">
       <c r="C230" s="2" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
     </row>
     <row r="231" ht="12.75" customHeight="1">
+      <c r="B231" s="2" t="s">
+        <v>230</v>
+      </c>
       <c r="C231" s="2" t="s">
-        <v>34</v>
+        <v>231</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E231" s="2">
+        <v>58.0</v>
       </c>
     </row>
     <row r="232" ht="12.75" customHeight="1">
-      <c r="B232" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="C232" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D232" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E232" s="2">
-        <v>62.0</v>
+        <v>232</v>
       </c>
     </row>
     <row r="233" ht="12.75" customHeight="1">
       <c r="C233" s="2" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
     </row>
     <row r="234" ht="12.75" customHeight="1">
       <c r="C234" s="2" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="235" ht="12.75" customHeight="1">
+      <c r="B235" s="2" t="s">
+        <v>235</v>
+      </c>
       <c r="C235" s="2" t="s">
-        <v>250</v>
+        <v>236</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E235" s="2">
+        <v>59.0</v>
       </c>
     </row>
     <row r="236" ht="12.75" customHeight="1">
-      <c r="B236" s="2" t="s">
-        <v>251</v>
-      </c>
       <c r="C236" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D236" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E236" s="2">
-        <v>63.0</v>
+        <v>237</v>
       </c>
     </row>
     <row r="237" ht="12.75" customHeight="1">
       <c r="C237" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="238" ht="12.75" customHeight="1">
       <c r="C238" s="2" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
     </row>
     <row r="239" ht="12.75" customHeight="1">
+      <c r="B239" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="C239" s="2" t="s">
-        <v>255</v>
+        <v>241</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E239" s="2">
+        <v>60.0</v>
       </c>
     </row>
     <row r="240" ht="12.75" customHeight="1">
-      <c r="B240" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="C240" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D240" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E240" s="2">
-        <v>64.0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="241" ht="12.75" customHeight="1">
       <c r="C241" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="242" ht="12.75" customHeight="1">
       <c r="C242" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="243" ht="12.75" customHeight="1">
+      <c r="A243" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>245</v>
+      </c>
       <c r="C243" s="2" t="s">
-        <v>260</v>
+        <v>32</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E243" s="2">
+        <v>61.0</v>
+      </c>
+      <c r="F243" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="244" ht="12.75" customHeight="1">
-      <c r="B244" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="C244" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D244" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E244" s="2">
-        <v>65.0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="245" ht="12.75" customHeight="1">
       <c r="C245" s="2" t="s">
-        <v>263</v>
+        <v>33</v>
       </c>
     </row>
     <row r="246" ht="12.75" customHeight="1">
       <c r="C246" s="2" t="s">
-        <v>264</v>
+        <v>34</v>
       </c>
     </row>
     <row r="247" ht="12.75" customHeight="1">
+      <c r="B247" s="2" t="s">
+        <v>246</v>
+      </c>
       <c r="C247" s="2" t="s">
-        <v>265</v>
+        <v>247</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E247" s="2">
+        <v>62.0</v>
       </c>
     </row>
     <row r="248" ht="12.75" customHeight="1">
-      <c r="A248" s="2">
-        <v>14.0</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>266</v>
-      </c>
       <c r="C248" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D248" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E248" s="2">
-        <v>66.0</v>
-      </c>
-      <c r="F248" s="2">
-        <v>0.0</v>
+        <v>248</v>
       </c>
     </row>
     <row r="249" ht="12.75" customHeight="1">
       <c r="C249" s="2" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
     </row>
     <row r="250" ht="12.75" customHeight="1">
       <c r="C250" s="2" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
     </row>
     <row r="251" ht="12.75" customHeight="1">
+      <c r="B251" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="C251" s="2" t="s">
-        <v>270</v>
+        <v>252</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E251" s="2">
+        <v>63.0</v>
       </c>
     </row>
     <row r="252" ht="12.75" customHeight="1">
-      <c r="B252" s="2" t="s">
-        <v>271</v>
-      </c>
       <c r="C252" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D252" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E252" s="2">
-        <v>67.0</v>
+        <v>253</v>
       </c>
     </row>
     <row r="253" ht="12.75" customHeight="1">
       <c r="C253" s="2" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
     </row>
     <row r="254" ht="12.75" customHeight="1">
       <c r="C254" s="2" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
     </row>
     <row r="255" ht="12.75" customHeight="1">
+      <c r="B255" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="C255" s="2" t="s">
-        <v>275</v>
+        <v>257</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E255" s="2">
+        <v>64.0</v>
       </c>
     </row>
     <row r="256" ht="12.75" customHeight="1">
-      <c r="B256" s="2" t="s">
-        <v>276</v>
-      </c>
       <c r="C256" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D256" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E256" s="2">
-        <v>68.0</v>
+        <v>258</v>
       </c>
     </row>
     <row r="257" ht="12.75" customHeight="1">
       <c r="C257" s="2" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
     </row>
     <row r="258" ht="12.75" customHeight="1">
       <c r="C258" s="2" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
     </row>
     <row r="259" ht="12.75" customHeight="1">
+      <c r="B259" s="2" t="s">
+        <v>261</v>
+      </c>
       <c r="C259" s="2" t="s">
-        <v>275</v>
+        <v>262</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E259" s="2">
+        <v>65.0</v>
       </c>
     </row>
     <row r="260" ht="12.75" customHeight="1">
-      <c r="B260" s="2" t="s">
-        <v>277</v>
-      </c>
       <c r="C260" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D260" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E260" s="2">
-        <v>69.0</v>
+        <v>263</v>
       </c>
     </row>
     <row r="261" ht="12.75" customHeight="1">
       <c r="C261" s="2" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
     </row>
     <row r="262" ht="12.75" customHeight="1">
       <c r="C262" s="2" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
     </row>
     <row r="263" ht="12.75" customHeight="1">
+      <c r="A263" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>266</v>
+      </c>
       <c r="C263" s="2" t="s">
-        <v>281</v>
+        <v>267</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E263" s="2">
+        <v>66.0</v>
+      </c>
+      <c r="F263" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="264" ht="12.75" customHeight="1">
-      <c r="B264" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="C264" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E264" s="2">
-        <v>70.0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="265" ht="12.75" customHeight="1">
       <c r="C265" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="266" ht="12.75" customHeight="1">
       <c r="C266" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="267" ht="12.75" customHeight="1">
+      <c r="B267" s="2" t="s">
+        <v>271</v>
+      </c>
       <c r="C267" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E267" s="2">
+        <v>67.0</v>
       </c>
     </row>
     <row r="268" ht="12.75" customHeight="1">
-      <c r="A268" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>283</v>
-      </c>
       <c r="C268" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D268" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E268" s="2">
-        <v>71.0</v>
-      </c>
-      <c r="F268" s="2">
-        <v>0.0</v>
+        <v>273</v>
       </c>
     </row>
     <row r="269" ht="12.75" customHeight="1">
       <c r="C269" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="270" ht="12.75" customHeight="1">
       <c r="C270" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="271" ht="12.75" customHeight="1">
+      <c r="B271" s="2" t="s">
+        <v>276</v>
+      </c>
       <c r="C271" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E271" s="2">
+        <v>68.0</v>
       </c>
     </row>
     <row r="272" ht="12.75" customHeight="1">
-      <c r="B272" s="2" t="s">
-        <v>284</v>
-      </c>
       <c r="C272" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D272" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E272" s="2">
-        <v>72.0</v>
+        <v>273</v>
       </c>
     </row>
     <row r="273" ht="12.75" customHeight="1">
       <c r="C273" s="2" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="274" ht="12.75" customHeight="1">
       <c r="C274" s="2" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="275" ht="12.75" customHeight="1">
+      <c r="B275" s="2" t="s">
+        <v>277</v>
+      </c>
       <c r="C275" s="2" t="s">
-        <v>288</v>
+        <v>278</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E275" s="2">
+        <v>69.0</v>
       </c>
     </row>
     <row r="276" ht="12.75" customHeight="1">
-      <c r="B276" s="2" t="s">
-        <v>289</v>
-      </c>
       <c r="C276" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D276" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E276" s="2">
-        <v>73.0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="277" ht="12.75" customHeight="1">
       <c r="C277" s="2" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="278" ht="12.75" customHeight="1">
       <c r="C278" s="2" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
     </row>
     <row r="279" ht="12.75" customHeight="1">
+      <c r="B279" s="3" t="s">
+        <v>282</v>
+      </c>
       <c r="C279" s="2" t="s">
-        <v>293</v>
+        <v>272</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E279" s="2">
+        <v>70.0</v>
       </c>
     </row>
     <row r="280" ht="12.75" customHeight="1">
-      <c r="B280" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="C280" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E280" s="2">
-        <v>74.0</v>
+        <v>273</v>
       </c>
     </row>
     <row r="281" ht="12.75" customHeight="1">
       <c r="C281" s="2" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="282" ht="12.75" customHeight="1">
       <c r="C282" s="2" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="283" ht="12.75" customHeight="1">
+      <c r="A283" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>283</v>
+      </c>
       <c r="C283" s="2" t="s">
-        <v>288</v>
+        <v>272</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E283" s="2">
+        <v>71.0</v>
+      </c>
+      <c r="F283" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="284" ht="12.75" customHeight="1">
-      <c r="B284" s="2" t="s">
-        <v>295</v>
-      </c>
       <c r="C284" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E284" s="2">
-        <v>75.0</v>
+        <v>273</v>
       </c>
     </row>
     <row r="285" ht="12.75" customHeight="1">
       <c r="C285" s="2" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="286" ht="12.75" customHeight="1">
       <c r="C286" s="2" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="287" ht="12.75" customHeight="1">
+      <c r="B287" s="2" t="s">
+        <v>284</v>
+      </c>
       <c r="C287" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E287" s="2">
+        <v>72.0</v>
       </c>
     </row>
     <row r="288" ht="12.75" customHeight="1">
-      <c r="A288" s="2">
-        <v>16.0</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>296</v>
-      </c>
       <c r="C288" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D288" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E288" s="2">
-        <v>76.0</v>
-      </c>
-      <c r="F288" s="2">
-        <v>0.0</v>
+        <v>286</v>
       </c>
     </row>
     <row r="289" ht="12.75" customHeight="1">
       <c r="C289" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="290" ht="12.75" customHeight="1">
       <c r="C290" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="291" ht="12.75" customHeight="1">
+      <c r="B291" s="2" t="s">
+        <v>289</v>
+      </c>
       <c r="C291" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E291" s="2">
+        <v>73.0</v>
       </c>
     </row>
     <row r="292" ht="12.75" customHeight="1">
-      <c r="B292" s="2" t="s">
-        <v>297</v>
-      </c>
       <c r="C292" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D292" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E292" s="2">
-        <v>77.0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="293" ht="12.75" customHeight="1">
       <c r="C293" s="2" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="294" ht="12.75" customHeight="1">
-      <c r="C294" s="3" t="s">
-        <v>300</v>
+      <c r="C294" s="2" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="295" ht="12.75" customHeight="1">
+      <c r="B295" s="2" t="s">
+        <v>294</v>
+      </c>
       <c r="C295" s="2" t="s">
-        <v>301</v>
+        <v>285</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E295" s="2">
+        <v>74.0</v>
       </c>
     </row>
     <row r="296" ht="12.75" customHeight="1">
-      <c r="B296" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="C296" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D296" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E296" s="2">
-        <v>78.0</v>
+        <v>286</v>
       </c>
     </row>
     <row r="297" ht="12.75" customHeight="1">
       <c r="C297" s="2" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
     </row>
     <row r="298" ht="12.75" customHeight="1">
       <c r="C298" s="2" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
     </row>
     <row r="299" ht="12.75" customHeight="1">
+      <c r="B299" s="2" t="s">
+        <v>295</v>
+      </c>
       <c r="C299" s="2" t="s">
-        <v>306</v>
+        <v>285</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E299" s="2">
+        <v>75.0</v>
       </c>
     </row>
     <row r="300" ht="12.75" customHeight="1">
-      <c r="B300" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="C300" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="D300" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E300" s="2">
-        <v>79.0</v>
+        <v>286</v>
       </c>
     </row>
     <row r="301" ht="12.75" customHeight="1">
       <c r="C301" s="2" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
     </row>
     <row r="302" ht="12.75" customHeight="1">
       <c r="C302" s="2" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
     </row>
     <row r="303" ht="12.75" customHeight="1">
+      <c r="A303" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>296</v>
+      </c>
       <c r="C303" s="2" t="s">
-        <v>311</v>
+        <v>285</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E303" s="2">
+        <v>76.0</v>
+      </c>
+      <c r="F303" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="304" ht="12.75" customHeight="1">
-      <c r="B304" s="2" t="s">
-        <v>312</v>
-      </c>
       <c r="C304" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D304" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E304" s="2">
-        <v>80.0</v>
+        <v>286</v>
       </c>
     </row>
     <row r="305" ht="12.75" customHeight="1">
       <c r="C305" s="2" t="s">
-        <v>314</v>
+        <v>287</v>
       </c>
     </row>
     <row r="306" ht="12.75" customHeight="1">
       <c r="C306" s="2" t="s">
-        <v>315</v>
+        <v>288</v>
       </c>
     </row>
     <row r="307" ht="12.75" customHeight="1">
+      <c r="B307" s="2" t="s">
+        <v>297</v>
+      </c>
       <c r="C307" s="2" t="s">
-        <v>316</v>
+        <v>298</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E307" s="2">
+        <v>77.0</v>
       </c>
     </row>
     <row r="308" ht="12.75" customHeight="1">
-      <c r="A308" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>317</v>
-      </c>
       <c r="C308" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D308" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E308" s="2">
-        <v>81.0</v>
-      </c>
-      <c r="F308" s="2">
-        <v>0.0</v>
+        <v>299</v>
       </c>
     </row>
     <row r="309" ht="12.75" customHeight="1">
-      <c r="C309" s="2" t="s">
-        <v>319</v>
+      <c r="C309" s="3" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="310" ht="12.75" customHeight="1">
       <c r="C310" s="2" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
     </row>
     <row r="311" ht="12.75" customHeight="1">
+      <c r="B311" s="2" t="s">
+        <v>302</v>
+      </c>
       <c r="C311" s="2" t="s">
-        <v>321</v>
+        <v>303</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E311" s="2">
+        <v>78.0</v>
       </c>
     </row>
     <row r="312" ht="12.75" customHeight="1">
-      <c r="B312" s="2" t="s">
-        <v>322</v>
-      </c>
       <c r="C312" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D312" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E312" s="2">
-        <v>82.0</v>
+        <v>304</v>
       </c>
     </row>
     <row r="313" ht="12.75" customHeight="1">
       <c r="C313" s="2" t="s">
-        <v>102</v>
+        <v>305</v>
       </c>
     </row>
     <row r="314" ht="12.75" customHeight="1">
       <c r="C314" s="2" t="s">
-        <v>101</v>
+        <v>306</v>
       </c>
     </row>
     <row r="315" ht="12.75" customHeight="1">
+      <c r="B315" s="2" t="s">
+        <v>307</v>
+      </c>
       <c r="C315" s="2" t="s">
-        <v>323</v>
+        <v>308</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E315" s="2">
+        <v>79.0</v>
       </c>
     </row>
     <row r="316" ht="12.75" customHeight="1">
-      <c r="B316" s="2" t="s">
-        <v>324</v>
-      </c>
       <c r="C316" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="D316" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E316" s="2">
-        <v>83.0</v>
+        <v>309</v>
       </c>
     </row>
     <row r="317" ht="12.75" customHeight="1">
       <c r="C317" s="2" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
     </row>
     <row r="318" ht="12.75" customHeight="1">
       <c r="C318" s="2" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
     </row>
     <row r="319" ht="12.75" customHeight="1">
+      <c r="B319" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="C319" s="2" t="s">
-        <v>328</v>
+        <v>313</v>
+      </c>
+      <c r="D319" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E319" s="2">
+        <v>80.0</v>
       </c>
     </row>
     <row r="320" ht="12.75" customHeight="1">
-      <c r="B320" s="2" t="s">
-        <v>329</v>
-      </c>
       <c r="C320" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D320" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E320" s="2">
-        <v>84.0</v>
+        <v>314</v>
       </c>
     </row>
     <row r="321" ht="12.75" customHeight="1">
       <c r="C321" s="2" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
     </row>
     <row r="322" ht="12.75" customHeight="1">
       <c r="C322" s="2" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
     </row>
     <row r="323" ht="12.75" customHeight="1">
+      <c r="A323" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>317</v>
+      </c>
       <c r="C323" s="2" t="s">
-        <v>333</v>
+        <v>318</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E323" s="2">
+        <v>81.0</v>
+      </c>
+      <c r="F323" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="324" ht="12.75" customHeight="1">
-      <c r="B324" s="2" t="s">
-        <v>334</v>
-      </c>
       <c r="C324" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="D324" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E324" s="2">
-        <v>85.0</v>
+        <v>319</v>
       </c>
     </row>
     <row r="325" ht="12.75" customHeight="1">
       <c r="C325" s="2" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
     </row>
     <row r="326" ht="12.75" customHeight="1">
       <c r="C326" s="2" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
     </row>
     <row r="327" ht="12.75" customHeight="1">
+      <c r="B327" s="2" t="s">
+        <v>322</v>
+      </c>
       <c r="C327" s="2" t="s">
-        <v>338</v>
+        <v>107</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E327" s="2">
+        <v>82.0</v>
       </c>
     </row>
     <row r="328" ht="12.75" customHeight="1">
-      <c r="A328" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="B328" s="2" t="s">
-        <v>339</v>
-      </c>
       <c r="C328" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D328" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E328" s="2">
-        <v>86.0</v>
-      </c>
-      <c r="F328" s="2">
-        <v>0.0</v>
+        <v>102</v>
       </c>
     </row>
     <row r="329" ht="12.75" customHeight="1">
       <c r="C329" s="2" t="s">
-        <v>340</v>
+        <v>101</v>
       </c>
     </row>
     <row r="330" ht="12.75" customHeight="1">
@@ -4466,443 +4439,545 @@
       </c>
     </row>
     <row r="331" ht="12.75" customHeight="1">
+      <c r="B331" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="C331" s="2" t="s">
-        <v>71</v>
+        <v>325</v>
+      </c>
+      <c r="D331" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E331" s="2">
+        <v>83.0</v>
       </c>
     </row>
     <row r="332" ht="12.75" customHeight="1">
-      <c r="B332" s="2" t="s">
-        <v>341</v>
-      </c>
       <c r="C332" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D332" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E332" s="2">
-        <v>87.0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="333" ht="12.75" customHeight="1">
       <c r="C333" s="2" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
     </row>
     <row r="334" ht="12.75" customHeight="1">
       <c r="C334" s="2" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
     </row>
     <row r="335" ht="12.75" customHeight="1">
+      <c r="B335" s="2" t="s">
+        <v>329</v>
+      </c>
       <c r="C335" s="2" t="s">
-        <v>345</v>
+        <v>330</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E335" s="2">
+        <v>84.0</v>
       </c>
     </row>
     <row r="336" ht="12.75" customHeight="1">
-      <c r="B336" s="2" t="s">
-        <v>346</v>
-      </c>
       <c r="C336" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D336" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E336" s="2">
-        <v>88.0</v>
+        <v>331</v>
       </c>
     </row>
     <row r="337" ht="12.75" customHeight="1">
       <c r="C337" s="2" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
     </row>
     <row r="338" ht="12.75" customHeight="1">
       <c r="C338" s="2" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
     </row>
     <row r="339" ht="12.75" customHeight="1">
+      <c r="B339" s="2" t="s">
+        <v>334</v>
+      </c>
       <c r="C339" s="2" t="s">
-        <v>350</v>
+        <v>335</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E339" s="2">
+        <v>85.0</v>
       </c>
     </row>
     <row r="340" ht="12.75" customHeight="1">
-      <c r="B340" s="2" t="s">
-        <v>351</v>
-      </c>
       <c r="C340" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D340" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E340" s="2">
-        <v>89.0</v>
+        <v>336</v>
       </c>
     </row>
     <row r="341" ht="12.75" customHeight="1">
       <c r="C341" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
     </row>
     <row r="342" ht="12.75" customHeight="1">
       <c r="C342" s="2" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
     </row>
     <row r="343" ht="12.75" customHeight="1">
+      <c r="A343" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>339</v>
+      </c>
       <c r="C343" s="2" t="s">
-        <v>355</v>
+        <v>32</v>
+      </c>
+      <c r="D343" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E343" s="2">
+        <v>86.0</v>
+      </c>
+      <c r="F343" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="344" ht="12.75" customHeight="1">
-      <c r="B344" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="C344" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D344" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E344" s="2">
-        <v>90.0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="345" ht="12.75" customHeight="1">
       <c r="C345" s="2" t="s">
-        <v>358</v>
+        <v>323</v>
       </c>
     </row>
     <row r="346" ht="12.75" customHeight="1">
       <c r="C346" s="2" t="s">
-        <v>359</v>
+        <v>71</v>
       </c>
     </row>
     <row r="347" ht="12.75" customHeight="1">
+      <c r="B347" s="2" t="s">
+        <v>341</v>
+      </c>
       <c r="C347" s="2" t="s">
-        <v>360</v>
+        <v>342</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E347" s="2">
+        <v>87.0</v>
       </c>
     </row>
     <row r="348" ht="12.75" customHeight="1">
-      <c r="A348" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="B348" s="2" t="s">
-        <v>361</v>
-      </c>
       <c r="C348" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D348" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E348" s="2">
-        <v>91.0</v>
-      </c>
-      <c r="F348" s="2">
-        <v>0.0</v>
+        <v>343</v>
       </c>
     </row>
     <row r="349" ht="12.75" customHeight="1">
       <c r="C349" s="2" t="s">
-        <v>363</v>
+        <v>344</v>
       </c>
     </row>
     <row r="350" ht="12.75" customHeight="1">
       <c r="C350" s="2" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
     </row>
     <row r="351" ht="12.75" customHeight="1">
+      <c r="B351" s="2" t="s">
+        <v>346</v>
+      </c>
       <c r="C351" s="2" t="s">
-        <v>365</v>
+        <v>347</v>
+      </c>
+      <c r="D351" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E351" s="2">
+        <v>88.0</v>
       </c>
     </row>
     <row r="352" ht="12.75" customHeight="1">
-      <c r="B352" s="2" t="s">
-        <v>366</v>
-      </c>
       <c r="C352" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="D352" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E352" s="2">
-        <v>92.0</v>
+        <v>348</v>
       </c>
     </row>
     <row r="353" ht="12.75" customHeight="1">
       <c r="C353" s="2" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
     </row>
     <row r="354" ht="12.75" customHeight="1">
       <c r="C354" s="2" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
     </row>
     <row r="355" ht="12.75" customHeight="1">
+      <c r="B355" s="2" t="s">
+        <v>351</v>
+      </c>
       <c r="C355" s="2" t="s">
-        <v>370</v>
+        <v>352</v>
+      </c>
+      <c r="D355" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E355" s="2">
+        <v>89.0</v>
       </c>
     </row>
     <row r="356" ht="12.75" customHeight="1">
-      <c r="B356" s="2" t="s">
-        <v>371</v>
-      </c>
       <c r="C356" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="D356" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E356" s="2">
-        <v>93.0</v>
+        <v>353</v>
       </c>
     </row>
     <row r="357" ht="12.75" customHeight="1">
       <c r="C357" s="2" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
     </row>
     <row r="358" ht="12.75" customHeight="1">
       <c r="C358" s="2" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
     </row>
     <row r="359" ht="12.75" customHeight="1">
+      <c r="B359" s="2" t="s">
+        <v>356</v>
+      </c>
       <c r="C359" s="2" t="s">
-        <v>375</v>
+        <v>357</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E359" s="2">
+        <v>90.0</v>
       </c>
     </row>
     <row r="360" ht="12.75" customHeight="1">
-      <c r="B360" s="2" t="s">
-        <v>376</v>
-      </c>
       <c r="C360" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="D360" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E360" s="2">
-        <v>94.0</v>
+        <v>358</v>
       </c>
     </row>
     <row r="361" ht="12.75" customHeight="1">
       <c r="C361" s="2" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
     </row>
     <row r="362" ht="12.75" customHeight="1">
       <c r="C362" s="2" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
     </row>
     <row r="363" ht="12.75" customHeight="1">
+      <c r="A363" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>361</v>
+      </c>
       <c r="C363" s="2" t="s">
-        <v>380</v>
+        <v>362</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E363" s="2">
+        <v>91.0</v>
+      </c>
+      <c r="F363" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="364" ht="12.75" customHeight="1">
-      <c r="B364" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="C364" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="D364" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E364" s="2">
-        <v>95.0</v>
+        <v>363</v>
       </c>
     </row>
     <row r="365" ht="12.75" customHeight="1">
       <c r="C365" s="2" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
     </row>
     <row r="366" ht="12.75" customHeight="1">
       <c r="C366" s="2" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
     </row>
     <row r="367" ht="12.75" customHeight="1">
+      <c r="B367" s="2" t="s">
+        <v>366</v>
+      </c>
       <c r="C367" s="2" t="s">
-        <v>385</v>
+        <v>367</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E367" s="2">
+        <v>92.0</v>
       </c>
     </row>
     <row r="368" ht="12.75" customHeight="1">
-      <c r="A368" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="B368" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="C368" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="D368" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E368" s="2">
-        <v>96.0</v>
-      </c>
-      <c r="F368" s="2">
-        <v>0.0</v>
+        <v>368</v>
       </c>
     </row>
     <row r="369" ht="12.75" customHeight="1">
       <c r="C369" s="2" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
     </row>
     <row r="370" ht="12.75" customHeight="1">
       <c r="C370" s="2" t="s">
-        <v>389</v>
+        <v>370</v>
       </c>
     </row>
     <row r="371" ht="12.75" customHeight="1">
+      <c r="B371" s="2" t="s">
+        <v>371</v>
+      </c>
       <c r="C371" s="2" t="s">
-        <v>390</v>
+        <v>372</v>
+      </c>
+      <c r="D371" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E371" s="2">
+        <v>93.0</v>
       </c>
     </row>
     <row r="372" ht="12.75" customHeight="1">
-      <c r="B372" s="2" t="s">
-        <v>391</v>
-      </c>
       <c r="C372" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D372" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E372" s="2">
-        <v>97.0</v>
+        <v>373</v>
       </c>
     </row>
     <row r="373" ht="12.75" customHeight="1">
       <c r="C373" s="2" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
     </row>
     <row r="374" ht="12.75" customHeight="1">
       <c r="C374" s="2" t="s">
-        <v>228</v>
+        <v>375</v>
       </c>
     </row>
     <row r="375" ht="12.75" customHeight="1">
+      <c r="B375" s="2" t="s">
+        <v>376</v>
+      </c>
       <c r="C375" s="2" t="s">
-        <v>394</v>
+        <v>377</v>
+      </c>
+      <c r="D375" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E375" s="2">
+        <v>94.0</v>
       </c>
     </row>
     <row r="376" ht="12.75" customHeight="1">
-      <c r="B376" s="2" t="s">
-        <v>395</v>
-      </c>
       <c r="C376" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="D376" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E376" s="2">
-        <v>98.0</v>
+        <v>378</v>
       </c>
     </row>
     <row r="377" ht="12.75" customHeight="1">
       <c r="C377" s="2" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
     </row>
     <row r="378" ht="12.75" customHeight="1">
       <c r="C378" s="2" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
     </row>
     <row r="379" ht="12.75" customHeight="1">
+      <c r="B379" s="2" t="s">
+        <v>381</v>
+      </c>
       <c r="C379" s="2" t="s">
-        <v>399</v>
+        <v>382</v>
+      </c>
+      <c r="D379" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E379" s="2">
+        <v>95.0</v>
       </c>
     </row>
     <row r="380" ht="12.75" customHeight="1">
-      <c r="B380" s="2" t="s">
-        <v>400</v>
-      </c>
       <c r="C380" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D380" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E380" s="2">
-        <v>99.0</v>
+        <v>383</v>
       </c>
     </row>
     <row r="381" ht="12.75" customHeight="1">
       <c r="C381" s="2" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
     </row>
     <row r="382" ht="12.75" customHeight="1">
       <c r="C382" s="2" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
     </row>
     <row r="383" ht="12.75" customHeight="1">
+      <c r="A383" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>386</v>
+      </c>
       <c r="C383" s="2" t="s">
-        <v>404</v>
+        <v>387</v>
+      </c>
+      <c r="D383" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E383" s="2">
+        <v>96.0</v>
+      </c>
+      <c r="F383" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="384" ht="12.75" customHeight="1">
-      <c r="B384" s="2" t="s">
-        <v>405</v>
-      </c>
       <c r="C384" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="D384" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E384" s="2">
-        <v>100.0</v>
+        <v>388</v>
       </c>
     </row>
     <row r="385" ht="12.75" customHeight="1">
       <c r="C385" s="2" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
     </row>
     <row r="386" ht="12.75" customHeight="1">
       <c r="C386" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="387" ht="12.75" customHeight="1">
+      <c r="B387" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D387" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E387" s="2">
+        <v>97.0</v>
+      </c>
+    </row>
+    <row r="388" ht="12.75" customHeight="1">
+      <c r="C388" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="389" ht="12.75" customHeight="1">
+      <c r="C389" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="390" ht="12.75" customHeight="1">
+      <c r="C390" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="391" ht="12.75" customHeight="1">
+      <c r="B391" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D391" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E391" s="2">
+        <v>98.0</v>
+      </c>
+    </row>
+    <row r="392" ht="12.75" customHeight="1">
+      <c r="C392" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="393" ht="12.75" customHeight="1">
+      <c r="C393" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="394" ht="12.75" customHeight="1">
+      <c r="C394" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="395" ht="12.75" customHeight="1">
+      <c r="B395" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C395" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D395" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E395" s="2">
+        <v>99.0</v>
+      </c>
+    </row>
+    <row r="396" ht="12.75" customHeight="1">
+      <c r="C396" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="397" ht="12.75" customHeight="1">
+      <c r="C397" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="398" ht="12.75" customHeight="1">
+      <c r="C398" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="399" ht="12.75" customHeight="1">
+      <c r="B399" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D399" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E399" s="2">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="400" ht="12.75" customHeight="1">
+      <c r="C400" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="401" ht="12.75" customHeight="1">
+      <c r="C401" s="2" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="387" ht="12.75" customHeight="1">
-      <c r="C387" s="2" t="s">
+    <row r="402" ht="12.75" customHeight="1">
+      <c r="C402" s="2" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="388" ht="12.75" customHeight="1"/>
-    <row r="389" ht="12.75" customHeight="1"/>
-    <row r="390" ht="12.75" customHeight="1"/>
-    <row r="391" ht="12.75" customHeight="1"/>
-    <row r="392" ht="12.75" customHeight="1"/>
-    <row r="393" ht="12.75" customHeight="1"/>
-    <row r="394" ht="12.75" customHeight="1"/>
-    <row r="395" ht="12.75" customHeight="1"/>
-    <row r="396" ht="12.75" customHeight="1"/>
-    <row r="397" ht="12.75" customHeight="1"/>
-    <row r="398" ht="12.75" customHeight="1"/>
-    <row r="399" ht="12.75" customHeight="1"/>
-    <row r="400" ht="12.75" customHeight="1"/>
-    <row r="401" ht="12.75" customHeight="1"/>
-    <row r="402" ht="12.75" customHeight="1"/>
     <row r="403" ht="12.75" customHeight="1"/>
     <row r="404" ht="12.75" customHeight="1"/>
     <row r="405" ht="12.75" customHeight="1"/>
@@ -5501,11 +5576,26 @@
     <row r="998" ht="12.75" customHeight="1"/>
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
+    <row r="1001" ht="12.75" customHeight="1"/>
+    <row r="1002" ht="12.75" customHeight="1"/>
+    <row r="1003" ht="12.75" customHeight="1"/>
+    <row r="1004" ht="12.75" customHeight="1"/>
+    <row r="1005" ht="12.75" customHeight="1"/>
+    <row r="1006" ht="12.75" customHeight="1"/>
+    <row r="1007" ht="12.75" customHeight="1"/>
+    <row r="1008" ht="12.75" customHeight="1"/>
+    <row r="1009" ht="12.75" customHeight="1"/>
+    <row r="1010" ht="12.75" customHeight="1"/>
+    <row r="1011" ht="12.75" customHeight="1"/>
+    <row r="1012" ht="12.75" customHeight="1"/>
+    <row r="1013" ht="12.75" customHeight="1"/>
+    <row r="1014" ht="12.75" customHeight="1"/>
+    <row r="1015" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="C1:E1"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
